--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcastedu-my.sharepoint.com/personal/haydnblythe_magro_g52465_mcast_edu_mt/Documents/Bachelor of Science (Honours) in Computer Systems and Networks/Year 3/Dissertation/THESIS/Chapter 4 - Analysis/Data Collection Template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="816" documentId="13_ncr:1_{ECEB1674-B840-4609-85CA-5FB6D80694C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B7BEC0-6B44-4298-AAF4-CEC9EF4FE0D2}"/>
+  <xr:revisionPtr revIDLastSave="824" documentId="13_ncr:1_{ECEB1674-B840-4609-85CA-5FB6D80694C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27CE56CD-4A59-4DCC-913C-4221D9FDE24B}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="52">
   <si>
     <t>PREPARATION RUNS LOG  —  1 Full Sync + 4 Incremental Replications per Repetition</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t xml:space="preserve">Each repetition block contains 3 preparation runs (rows shaded blue) followed by 1 failover test (see Failover Results sheet). </t>
+  </si>
+  <si>
+    <t>180-240</t>
   </si>
 </sst>
 </file>
@@ -437,13 +440,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,10 +531,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,23 +749,23 @@
       <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
@@ -6535,22 +6534,22 @@
       <c r="P1" s="21"/>
     </row>
     <row r="2" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
@@ -7273,8 +7272,8 @@
       <c r="F17" s="11">
         <v>53</v>
       </c>
-      <c r="G17" s="11">
-        <v>60</v>
+      <c r="G17" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H17" s="11">
         <v>49.19</v>
@@ -7303,7 +7302,7 @@
       </c>
       <c r="P17" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
@@ -7325,8 +7324,8 @@
       <c r="F18" s="15">
         <v>53</v>
       </c>
-      <c r="G18" s="15">
-        <v>60</v>
+      <c r="G18" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H18" s="15">
         <v>45.69</v>
@@ -7355,7 +7354,7 @@
       </c>
       <c r="P18" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
@@ -7377,8 +7376,8 @@
       <c r="F19" s="11">
         <v>53</v>
       </c>
-      <c r="G19" s="11">
-        <v>60</v>
+      <c r="G19" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H19" s="11">
         <v>50.98</v>
@@ -7407,7 +7406,7 @@
       </c>
       <c r="P19" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -7429,8 +7428,8 @@
       <c r="F20" s="15">
         <v>47</v>
       </c>
-      <c r="G20" s="15">
-        <v>60</v>
+      <c r="G20" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H20" s="15">
         <v>43.64</v>
@@ -7459,7 +7458,7 @@
       </c>
       <c r="P20" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
@@ -7481,8 +7480,8 @@
       <c r="F21" s="11">
         <v>143</v>
       </c>
-      <c r="G21" s="11">
-        <v>60</v>
+      <c r="G21" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H21" s="11">
         <v>59.01</v>
@@ -7511,7 +7510,7 @@
       </c>
       <c r="P21" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
@@ -7533,8 +7532,8 @@
       <c r="F22" s="15">
         <v>78</v>
       </c>
-      <c r="G22" s="15">
-        <v>60</v>
+      <c r="G22" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H22" s="15">
         <v>41.03</v>
@@ -7563,7 +7562,7 @@
       </c>
       <c r="P22" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -7585,8 +7584,8 @@
       <c r="F23" s="11">
         <v>53</v>
       </c>
-      <c r="G23" s="11">
-        <v>60</v>
+      <c r="G23" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H23" s="11">
         <v>47.77</v>
@@ -7615,7 +7614,7 @@
       </c>
       <c r="P23" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
@@ -7637,8 +7636,8 @@
       <c r="F24" s="15">
         <v>58</v>
       </c>
-      <c r="G24" s="15">
-        <v>60</v>
+      <c r="G24" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H24" s="15">
         <v>46.39</v>
@@ -7667,7 +7666,7 @@
       </c>
       <c r="P24" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -7689,8 +7688,8 @@
       <c r="F25" s="11">
         <v>64</v>
       </c>
-      <c r="G25" s="11">
-        <v>60</v>
+      <c r="G25" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H25" s="11">
         <v>43.17</v>
@@ -7719,7 +7718,7 @@
       </c>
       <c r="P25" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
@@ -7741,8 +7740,8 @@
       <c r="F26" s="15">
         <v>54</v>
       </c>
-      <c r="G26" s="15">
-        <v>60</v>
+      <c r="G26" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H26" s="15">
         <v>52.67</v>
@@ -7771,7 +7770,7 @@
       </c>
       <c r="P26" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
@@ -7793,8 +7792,8 @@
       <c r="F27" s="11">
         <v>53</v>
       </c>
-      <c r="G27" s="11">
-        <v>60</v>
+      <c r="G27" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="H27" s="11">
         <v>44.44</v>
@@ -7823,7 +7822,7 @@
       </c>
       <c r="P27" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -7845,8 +7844,8 @@
       <c r="F28" s="15">
         <v>72</v>
       </c>
-      <c r="G28" s="15">
-        <v>60</v>
+      <c r="G28" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="H28" s="15">
         <v>53.88</v>
@@ -7875,7 +7874,7 @@
       </c>
       <c r="P28" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>✓ Met</v>
+        <v>-</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcastedu-my.sharepoint.com/personal/haydnblythe_magro_g52465_mcast_edu_mt/Documents/Bachelor of Science (Honours) in Computer Systems and Networks/Year 3/Dissertation/THESIS/Chapter 4 - Analysis/Data Collection Template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haydn Magro\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="824" documentId="13_ncr:1_{ECEB1674-B840-4609-85CA-5FB6D80694C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27CE56CD-4A59-4DCC-913C-4221D9FDE24B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E03329AB-E024-405F-A61F-4DE0BB606151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preparation Runs" sheetId="1" r:id="rId1"/>
@@ -101,10 +101,6 @@
   <si>
     <t>Mem Util | Primary
 (%)</t>
-  </si>
-  <si>
-    <t>Throughput
-(Mbps)</t>
   </si>
   <si>
     <t>Latency
@@ -223,6 +219,10 @@
   </si>
   <si>
     <t>180-240</t>
+  </si>
+  <si>
+    <t>Throughput
+(MB/s)</t>
   </si>
 </sst>
 </file>
@@ -750,7 +750,7 @@
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -827,16 +827,16 @@
         <v>15</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -847,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F5" s="16">
         <v>0.88541666666666663</v>
@@ -894,13 +894,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F6" s="18">
         <v>0.90694444444444444</v>
@@ -941,13 +941,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F7" s="16">
         <v>0.91874999999999996</v>
@@ -988,13 +988,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F8" s="18">
         <v>0.92986111111111114</v>
@@ -1035,13 +1035,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F9" s="16">
         <v>0.94097222222222221</v>
@@ -1082,13 +1082,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F10" s="18">
         <v>0.9604166666666667</v>
@@ -1129,13 +1129,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F11" s="16">
         <v>0.97638888888888886</v>
@@ -1176,13 +1176,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F12" s="18">
         <v>0.9868055555555556</v>
@@ -1223,13 +1223,13 @@
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F13" s="16">
         <v>0.99722222222222223</v>
@@ -1270,13 +1270,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F14" s="18">
         <v>6.9444444444444441E-3</v>
@@ -1317,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F15" s="16">
         <v>0.84166666666666667</v>
@@ -1364,13 +1364,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F16" s="18">
         <v>0.85902777777777772</v>
@@ -1411,13 +1411,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F17" s="16">
         <v>0.87152777777777779</v>
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="F18" s="18">
         <v>0.88472222222222219</v>
@@ -1505,13 +1505,13 @@
         <v>5</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="F19" s="16">
         <v>0.89513888888888893</v>
@@ -1552,13 +1552,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="18">
         <v>0.92083333333333328</v>
@@ -1599,13 +1599,13 @@
         <v>2</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="16">
         <v>0.95833333333333337</v>
@@ -1646,13 +1646,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="18">
         <v>0.96666666666666667</v>
@@ -1693,13 +1693,13 @@
         <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" s="16">
         <v>0.46041666666666664</v>
@@ -1740,13 +1740,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="F24" s="18">
         <v>0.47083333333333333</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="16">
         <v>0.60347222222222219</v>
@@ -1834,13 +1834,13 @@
         <v>2</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" s="18">
         <v>0.6333333333333333</v>
@@ -1881,13 +1881,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F27" s="16">
         <v>0.64861111111111114</v>
@@ -1928,13 +1928,13 @@
         <v>4</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F28" s="18">
         <v>0.65972222222222221</v>
@@ -1975,13 +1975,13 @@
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F29" s="16">
         <v>0.67152777777777772</v>
@@ -2022,13 +2022,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="18">
         <v>0.84375</v>
@@ -2069,13 +2069,13 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" s="16">
         <v>0.93055555555555558</v>
@@ -2116,13 +2116,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" s="18">
         <v>0.94097222222222221</v>
@@ -2163,13 +2163,13 @@
         <v>4</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" s="16">
         <v>0.95208333333333328</v>
@@ -2210,13 +2210,13 @@
         <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="F34" s="18">
         <v>0.96319444444444446</v>
@@ -2257,13 +2257,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F35" s="16">
         <v>0.88263888888888886</v>
@@ -2304,13 +2304,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F36" s="18">
         <v>0.44722222222222224</v>
@@ -2351,13 +2351,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F37" s="16">
         <v>0.45763888888888887</v>
@@ -2398,13 +2398,13 @@
         <v>4</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F38" s="18">
         <v>0.46805555555555556</v>
@@ -2445,13 +2445,13 @@
         <v>5</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F39" s="16">
         <v>0.4826388888888889</v>
@@ -2492,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F40" s="18">
         <v>0.50277777777777777</v>
@@ -2539,13 +2539,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F41" s="16">
         <v>0.79236111111111107</v>
@@ -2586,13 +2586,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F42" s="18">
         <v>0.81874999999999998</v>
@@ -2633,13 +2633,13 @@
         <v>4</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F43" s="16">
         <v>0.83125000000000004</v>
@@ -2680,13 +2680,13 @@
         <v>5</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F44" s="18">
         <v>0.84236111111111112</v>
@@ -2727,13 +2727,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F45" s="16">
         <v>0.85833333333333328</v>
@@ -2774,13 +2774,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F46" s="18">
         <v>0.94861111111111107</v>
@@ -2821,13 +2821,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F47" s="16">
         <v>0.98333333333333328</v>
@@ -2868,13 +2868,13 @@
         <v>4</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F48" s="18">
         <v>0.99513888888888891</v>
@@ -2915,13 +2915,13 @@
         <v>5</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F49" s="16">
         <v>5.5555555555555558E-3</v>
@@ -2962,13 +2962,13 @@
         <v>1</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F50" s="18">
         <v>0.86875000000000002</v>
@@ -3009,13 +3009,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F51" s="16">
         <v>0.38263888888888886</v>
@@ -3056,13 +3056,13 @@
         <v>3</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F52" s="18">
         <v>0.39652777777777776</v>
@@ -3103,13 +3103,13 @@
         <v>4</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F53" s="16">
         <v>0.40833333333333333</v>
@@ -3150,13 +3150,13 @@
         <v>5</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F54" s="18">
         <v>0.43402777777777779</v>
@@ -3197,13 +3197,13 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F55" s="16">
         <v>0.4513888888888889</v>
@@ -3244,13 +3244,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F56" s="18">
         <v>0.80069444444444449</v>
@@ -3291,13 +3291,13 @@
         <v>3</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F57" s="16">
         <v>0.81805555555555554</v>
@@ -3338,13 +3338,13 @@
         <v>4</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F58" s="18">
         <v>0.8305555555555556</v>
@@ -3385,13 +3385,13 @@
         <v>5</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F59" s="16">
         <v>0.84027777777777779</v>
@@ -3432,13 +3432,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F60" s="18">
         <v>0.85833333333333328</v>
@@ -3479,13 +3479,13 @@
         <v>2</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F61" s="16">
         <v>0.37152777777777779</v>
@@ -3526,13 +3526,13 @@
         <v>3</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F62" s="18">
         <v>0.38750000000000001</v>
@@ -3573,13 +3573,13 @@
         <v>4</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F63" s="16">
         <v>0.55347222222222225</v>
@@ -3620,13 +3620,13 @@
         <v>5</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F64" s="18">
         <v>0.56666666666666665</v>
@@ -3667,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F65" s="16">
         <v>0.68263888888888891</v>
@@ -3714,13 +3714,13 @@
         <v>2</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F66" s="18">
         <v>0.6958333333333333</v>
@@ -3761,13 +3761,13 @@
         <v>3</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" s="16">
         <v>0.69791666666666663</v>
@@ -3808,13 +3808,13 @@
         <v>4</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F68" s="18">
         <v>0.7006944444444444</v>
@@ -3855,13 +3855,13 @@
         <v>5</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F69" s="16">
         <v>0.70347222222222228</v>
@@ -3902,13 +3902,13 @@
         <v>1</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F70" s="8">
         <v>17.38</v>
@@ -3949,13 +3949,13 @@
         <v>2</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F71" s="16">
         <v>0.75</v>
@@ -3996,13 +3996,13 @@
         <v>3</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F72" s="18">
         <v>0.75208333333333333</v>
@@ -4043,13 +4043,13 @@
         <v>4</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F73" s="16">
         <v>0.75486111111111109</v>
@@ -4090,13 +4090,13 @@
         <v>5</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F74" s="18">
         <v>0.75694444444444442</v>
@@ -4137,13 +4137,13 @@
         <v>1</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F75" s="16">
         <v>0.78263888888888888</v>
@@ -4184,13 +4184,13 @@
         <v>2</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F76" s="18">
         <v>0.79583333333333328</v>
@@ -4231,13 +4231,13 @@
         <v>3</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F77" s="16">
         <v>0.79861111111111116</v>
@@ -4278,13 +4278,13 @@
         <v>4</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F78" s="18">
         <v>0.80069444444444449</v>
@@ -4325,13 +4325,13 @@
         <v>5</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F79" s="16">
         <v>0.80347222222222225</v>
@@ -4372,13 +4372,13 @@
         <v>1</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F80" s="18">
         <v>0.89444444444444449</v>
@@ -4419,13 +4419,13 @@
         <v>2</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F81" s="16">
         <v>0.94097222222222221</v>
@@ -4466,13 +4466,13 @@
         <v>3</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F82" s="18">
         <v>0.94444444444444442</v>
@@ -4513,13 +4513,13 @@
         <v>4</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F83" s="16">
         <v>0.94652777777777775</v>
@@ -4560,13 +4560,13 @@
         <v>5</v>
       </c>
       <c r="C84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="F84" s="18">
         <v>0.94930555555555551</v>
@@ -4607,13 +4607,13 @@
         <v>1</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F85" s="16">
         <v>0.79097222222222219</v>
@@ -4654,13 +4654,13 @@
         <v>2</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F86" s="18">
         <v>0.83263888888888893</v>
@@ -4701,13 +4701,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F87" s="16">
         <v>0.83611111111111114</v>
@@ -4748,13 +4748,13 @@
         <v>4</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F88" s="18">
         <v>0.83819444444444446</v>
@@ -4795,13 +4795,13 @@
         <v>5</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F89" s="16">
         <v>0.84097222222222223</v>
@@ -4842,13 +4842,13 @@
         <v>1</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F90" s="18">
         <v>0.88541666666666663</v>
@@ -4889,13 +4889,13 @@
         <v>2</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F91" s="16">
         <v>0.92083333333333328</v>
@@ -4936,13 +4936,13 @@
         <v>3</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F92" s="18">
         <v>0.92361111111111116</v>
@@ -4983,13 +4983,13 @@
         <v>4</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F93" s="16">
         <v>0.92569444444444449</v>
@@ -5030,13 +5030,13 @@
         <v>5</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="F94" s="18">
         <v>0.92847222222222225</v>
@@ -5077,13 +5077,13 @@
         <v>1</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F95" s="16">
         <v>0.90347222222222223</v>
@@ -5124,13 +5124,13 @@
         <v>2</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F96" s="18">
         <v>0.95347222222222228</v>
@@ -5171,13 +5171,13 @@
         <v>3</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F97" s="16">
         <v>0.9604166666666667</v>
@@ -5218,13 +5218,13 @@
         <v>4</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F98" s="18">
         <v>0.98819444444444449</v>
@@ -5265,13 +5265,13 @@
         <v>5</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F99" s="16">
         <v>0.99305555555555558</v>
@@ -5312,13 +5312,13 @@
         <v>1</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F100" s="18">
         <v>0.38333333333333336</v>
@@ -5359,13 +5359,13 @@
         <v>2</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F101" s="16">
         <v>0.41666666666666669</v>
@@ -5406,13 +5406,13 @@
         <v>3</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F102" s="18">
         <v>0.41944444444444445</v>
@@ -5453,13 +5453,13 @@
         <v>4</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F103" s="16">
         <v>0.42222222222222222</v>
@@ -5500,13 +5500,13 @@
         <v>5</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F104" s="18">
         <v>0.42499999999999999</v>
@@ -5547,13 +5547,13 @@
         <v>1</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F105" s="16">
         <v>0.94027777777777777</v>
@@ -5594,13 +5594,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F106" s="18">
         <v>0.99097222222222225</v>
@@ -5641,13 +5641,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F107" s="16">
         <v>0.99513888888888891</v>
@@ -5688,13 +5688,13 @@
         <v>4</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F108" s="18">
         <v>0.99791666666666667</v>
@@ -5735,13 +5735,13 @@
         <v>5</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F109" s="16">
         <v>6.9444444444444447E-4</v>
@@ -5782,13 +5782,13 @@
         <v>1</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F110" s="18">
         <v>0.48402777777777778</v>
@@ -5829,13 +5829,13 @@
         <v>2</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F111" s="16">
         <v>0.61111111111111116</v>
@@ -5876,13 +5876,13 @@
         <v>3</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F112" s="18">
         <v>0.61805555555555558</v>
@@ -5923,13 +5923,13 @@
         <v>4</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F113" s="16">
         <v>0.62152777777777779</v>
@@ -5970,13 +5970,13 @@
         <v>5</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F114" s="18">
         <v>0.62430555555555556</v>
@@ -6017,13 +6017,13 @@
         <v>1</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F115" s="16">
         <v>0.82152777777777775</v>
@@ -6064,13 +6064,13 @@
         <v>2</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F116" s="18">
         <v>0.93333333333333335</v>
@@ -6111,13 +6111,13 @@
         <v>3</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F117" s="16">
         <v>0.94166666666666665</v>
@@ -6158,13 +6158,13 @@
         <v>4</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F118" s="18">
         <v>0.94513888888888886</v>
@@ -6205,13 +6205,13 @@
         <v>5</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F119" s="16">
         <v>0.94791666666666663</v>
@@ -6252,13 +6252,13 @@
         <v>1</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F120" s="18">
         <v>0.70625000000000004</v>
@@ -6299,13 +6299,13 @@
         <v>2</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F121" s="16">
         <v>0.82708333333333328</v>
@@ -6346,13 +6346,13 @@
         <v>3</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F122" s="18">
         <v>0.83402777777777781</v>
@@ -6393,13 +6393,13 @@
         <v>4</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F123" s="16">
         <v>0.83819444444444446</v>
@@ -6440,13 +6440,13 @@
         <v>5</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F124" s="18">
         <v>0.84097222222222223</v>
@@ -6515,7 +6515,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -6560,28 +6560,28 @@
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
       <c r="F3" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="23"/>
       <c r="H3" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
       <c r="M3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P3" s="23"/>
     </row>
     <row r="4" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6593,19 +6593,19 @@
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>14</v>
@@ -6614,19 +6614,19 @@
         <v>15</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -6637,13 +6637,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>22</v>
-      </c>
       <c r="E5" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="11">
         <v>45</v>
@@ -6667,7 +6667,7 @@
         <v>1.378304</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="19">
         <v>0.94652777777777775</v>
@@ -6689,13 +6689,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>22</v>
-      </c>
       <c r="E6" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="15">
         <v>45</v>
@@ -6719,7 +6719,7 @@
         <v>1.1468799999999999</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="20">
         <v>1.5972222222222221E-2</v>
@@ -6741,13 +6741,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="11">
         <v>44</v>
@@ -6771,7 +6771,7 @@
         <v>1.435648</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" s="19">
         <v>0.91319444444444442</v>
@@ -6793,13 +6793,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F8" s="15">
         <v>44</v>
@@ -6823,7 +6823,7 @@
         <v>1.5329280000000001</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" s="20">
         <v>0.5756944444444444</v>
@@ -6845,13 +6845,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11">
         <v>44</v>
@@ -6875,7 +6875,7 @@
         <v>1.0250239999999999</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" s="19">
         <v>0.83125000000000004</v>
@@ -6897,13 +6897,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="15">
         <v>52</v>
@@ -6927,7 +6927,7 @@
         <v>1.2318720000000001</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="20">
         <v>0.87083333333333335</v>
@@ -6949,13 +6949,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="11">
         <v>74</v>
@@ -6979,7 +6979,7 @@
         <v>1.808384</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" s="19">
         <v>0.48749999999999999</v>
@@ -7001,13 +7001,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="15">
         <v>37</v>
@@ -7031,7 +7031,7 @@
         <v>2.6142720000000002</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="20">
         <v>0.84930555555555554</v>
@@ -7053,13 +7053,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="11">
         <v>43</v>
@@ -7083,7 +7083,7 @@
         <v>1.6721919999999999</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13" s="19">
         <v>0.85972222222222228</v>
@@ -7105,13 +7105,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="15">
         <v>45</v>
@@ -7135,7 +7135,7 @@
         <v>2.5989119999999999</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N14" s="20">
         <v>0.44097222222222221</v>
@@ -7157,13 +7157,13 @@
         <v>2</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="11">
         <v>42</v>
@@ -7187,7 +7187,7 @@
         <v>2.542592</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15" s="19">
         <v>0.84652777777777777</v>
@@ -7209,13 +7209,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="15">
         <v>46</v>
@@ -7239,7 +7239,7 @@
         <v>3.2880639999999999</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="20">
         <v>0.57291666666666663</v>
@@ -7261,19 +7261,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="11">
         <v>53</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17" s="11">
         <v>49.19</v>
@@ -7291,7 +7291,7 @@
         <v>1.027072</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="19">
         <v>0.72499999999999998</v>
@@ -7313,19 +7313,19 @@
         <v>2</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="15">
         <v>53</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="15">
         <v>45.69</v>
@@ -7343,7 +7343,7 @@
         <v>1.084416</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" s="20">
         <v>0.7729166666666667</v>
@@ -7365,19 +7365,19 @@
         <v>3</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="11">
         <v>53</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="11">
         <v>50.98</v>
@@ -7395,7 +7395,7 @@
         <v>1.0700799999999999</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="19">
         <v>0.82222222222222219</v>
@@ -7417,19 +7417,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" s="15">
         <v>47</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="15">
         <v>43.64</v>
@@ -7447,7 +7447,7 @@
         <v>1.1970559999999999</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="20">
         <v>0.97499999999999998</v>
@@ -7469,19 +7469,19 @@
         <v>2</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" s="11">
         <v>143</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H21" s="11">
         <v>59.01</v>
@@ -7499,7 +7499,7 @@
         <v>1.2308479999999999</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="19">
         <v>0.87291666666666667</v>
@@ -7521,19 +7521,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F22" s="15">
         <v>78</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="15">
         <v>41.03</v>
@@ -7551,7 +7551,7 @@
         <v>1.380352</v>
       </c>
       <c r="M22" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="20">
         <v>0.88958333333333328</v>
@@ -7573,19 +7573,19 @@
         <v>1</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23" s="11">
         <v>53</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H23" s="11">
         <v>47.77</v>
@@ -7603,7 +7603,7 @@
         <v>10.903551999999999</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N23" s="19">
         <v>0.82291666666666663</v>
@@ -7625,19 +7625,19 @@
         <v>2</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" s="15">
         <v>58</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="15">
         <v>46.39</v>
@@ -7655,7 +7655,7 @@
         <v>1.117184</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24" s="20">
         <v>0.84791666666666665</v>
@@ -7677,19 +7677,19 @@
         <v>3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" s="11">
         <v>64</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="11">
         <v>43.17</v>
@@ -7707,7 +7707,7 @@
         <v>1.164288</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="19">
         <v>0.47152777777777777</v>
@@ -7729,19 +7729,19 @@
         <v>1</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="15">
         <v>54</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15">
         <v>52.67</v>
@@ -7759,7 +7759,7 @@
         <v>1.5370239999999999</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="20">
         <v>0.80833333333333335</v>
@@ -7781,19 +7781,19 @@
         <v>2</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F27" s="11">
         <v>53</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="11">
         <v>44.44</v>
@@ -7811,7 +7811,7 @@
         <v>1.5196160000000001</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" s="19">
         <v>0.69236111111111109</v>
@@ -7833,19 +7833,19 @@
         <v>3</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" s="15">
         <v>72</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="15">
         <v>53.88</v>
@@ -7863,7 +7863,7 @@
         <v>1.570816</v>
       </c>
       <c r="M28" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="20">
         <v>0.87986111111111109</v>
